--- a/outputs/43589.xlsx
+++ b/outputs/43589.xlsx
@@ -337,7 +337,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="n">
-        <f aca="false">VALUE(MID(A2,FIND(" to ",A2)+4,10))-VALUE(LEFT(A2,FIND(" to ",A2)-1))+1</f>
+        <f aca="false">RIGHT(A2,LEN(A2)-FIND(" to ",A2)-3)-LEFT(A2,FIND(" to ",A2)-1)+1</f>
         <v>4</v>
       </c>
     </row>

--- a/outputs/43589.xlsx
+++ b/outputs/43589.xlsx
@@ -337,7 +337,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="n">
-        <f aca="false">RIGHT(A2,LEN(A2)-FIND(" to ",A2)-3)-LEFT(A2,FIND(" to ",A2)-1)+1</f>
+        <f aca="false">VALUE(MID(A2,FIND(" to ",A2)+4,100))-VALUE(LEFT(A2,FIND(" to ",A2)-1))+1</f>
         <v>4</v>
       </c>
     </row>
